--- a/data/daily/2026-10/2026-10-01.xlsx
+++ b/data/daily/2026-10/2026-10-01.xlsx
@@ -1195,14 +1195,114 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1217,17 +1317,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="323850" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1242,110 +1342,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>4</row>
+      <row>8</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>5</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="361950" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>6</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -1450,157 +1450,157 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="866775" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="990600" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -1827,7 +1827,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>7</row>
+      <row>8</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="457200" cy="457200"/>
@@ -1852,7 +1852,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>8</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="457200" cy="457200"/>
@@ -1877,7 +1877,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="457200" cy="457200"/>
@@ -1888,31 +1888,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>10</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="457200" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="10" name="Image 10" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId10"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2080,7 +2055,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>8</col>
+      <col>9</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -2105,7 +2080,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>9</col>
+      <col>10</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -2130,7 +2105,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>10</col>
+      <col>11</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -2143,31 +2118,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>11</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1238250" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="10" name="Image 10" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId10"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2596,29 +2546,25 @@
         <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>16172</v>
+        <v>16173</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>간편한 복용 방법 — 하루 한 번 액상과 정제를 함께 먹는 제형이라 간편함</t>
+          <t>피로 회복 및 체력 증진 — 섭취 후 피로감이 줄어들고 기력 및 면역력 향상에 도움을 줌</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>피로 회복 기대감 — 피로나 기력 저하 시 섭취하여 건강 관리에 도움이 됨</t>
+          <t>간편한 복용 방식 — 하루 한 번 액상과 정제를 함께 먹는 형태로 복용이 매우 간편함</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>용기 파손 발생 — 배송이나 이동 중 일부 제품 용기가 폭파 및 파손됨</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>단기 효과 미흡 — 가끔 먹는 단기 섭취 시 눈에 띄는 빠른 효과를 느끼기 어려움</t>
-        </is>
-      </c>
+          <t>제품 터짐 및 용기 하자 — 보관이나 이동 중 일부 용기가 폭발하듯 깨져 내용물이 새어나옴</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
     </row>
     <row r="3" ht="38" customHeight="1">
@@ -2659,26 +2605,22 @@
         <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>15506</v>
+        <v>15507</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>휴대 및 복용 편의 — 물 없이 가지고 다니며 피곤할 때 간편하게 먹기 좋음</t>
+          <t>체력 증진 및 피로 회복 — 수면 효율이 좋아지고 피로 회복과 체력 개선 효과가 뛰어남</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>맛과 풍미 만족 — 맛이 좋아 거부감 없이 맛있게 섭취가 가능함</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>빠르고 꼼꼼한 배송 — 배송이 빠르며 포장이 꼼꼼하게 처리되어 도착함</t>
-        </is>
-      </c>
+          <t>좋은 맛과 휴대 편의성 — 맛이 좋고 물 없이 챙겨 먹을 수 있어 휴대 및 복용이 용이함</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>공복 섭취 시 속 불편 — 빈속에 복용 시 울렁거림이나 구토 증상이 나타날 수 있음</t>
+          <t>공복 섭취 시 속 불편함 — 빈속에 복용 시 강한 속 울렁거림이나 구토 증상이 발생할 수 있음</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
@@ -2722,22 +2664,22 @@
         <v>4</v>
       </c>
       <c r="J4" t="n">
-        <v>3379</v>
+        <v>3381</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>선물용으로 적합 — 깔끔한 구성과 패키지로 명절이나 위로 선물로 좋음</t>
+          <t>선물용으로 높은 만족도 — 패키지가 깔끔하고 브랜드 인지도가 높아 선물용으로 적합함</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>활력 증진 도움 — 먹기 편하며 섭취 후 기운이 나는 느낌을 받음</t>
+          <t>피로 회복 및 활력 증진 — 섭취 시 피로 해소에 도움을 주고 섭취 방법이 편리함</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>완충재 부족 배송 — 완충제 없이 배송되어 제품 박스가 찌그러져 도착함</t>
+          <t>부실한 완충 포장 — 완충재 없이 포장되어 배송 중 상자가 찌그러져 도착함</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
@@ -2781,23 +2723,19 @@
         <v>4</v>
       </c>
       <c r="J5" t="n">
-        <v>6489</v>
+        <v>6490</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>젤리 제형의 편의성 — 구미 젤리 형태로 물 없이 간편하게 섭취 가능함</t>
+          <t>맛있는 구미 제형 — 마이구미처럼 맛이 좋아 거부감 없이 섭취할 수 있음</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>맛있는 맛과 식감 — 영양제 특유의 거부감 없이 젤리처럼 맛있게 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>귀여운 선물 패키지 — 포장이 깔끔하고 귀여워 가볍게 선물하기에 적합함</t>
-        </is>
-      </c>
+          <t>간편한 섭취 방식 — 알약을 못 먹는 사람도 물 없이 간편하게 챙겨 먹을 수 있음</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
@@ -2844,19 +2782,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>피로 회복 및 체력 관리 — 섭취 후 하루 종일 지치지 않고 기운을 차리는 데 도움 됨</t>
+          <t>신속한 피로 회복 — 체력 방전이나 피로감이 심할 때 빠르게 기운을 차리는 데 도움을 줌</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>고급스러운 포장 — 패키지가 예쁘고 정성스럽게 포장되어 선물용으로 훌륭함</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>합리적인 가격과 배송 — 저렴한 가격에 빠른 배송으로 받아서 만족함</t>
-        </is>
-      </c>
+          <t>예쁜 선물 패키지 — 패키지 구성이 예뻐서 선물로 받았을 때 기분이 좋아짐</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
@@ -2903,19 +2837,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>알찬 구성과 깔끔한 포장 — 증정품이 더해진 구성에 깔끔한 패키지라 선물하기 좋음</t>
+          <t>깔끔한 패키지 구성 — 단독 에디션 패키지가 깔끔하고 추가 증정 구성이 알참</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>기력 및 피로 회복 — 지치고 피곤할 때 간편히 챙겨 먹으며 기운을 얻음</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>올인원 간편 섭취 — 여러 영양제를 따로 챙길 필요 없이 한 번에 복용 가능함</t>
-        </is>
-      </c>
+          <t>기력 회복 및 간편성 — 지치고 피곤할 때 간편하게 챙겨 먹기 좋음</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
@@ -2958,26 +2888,22 @@
         <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>1713</v>
+        <v>1715</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>목넘김과 기호성 — 과하게 시지 않고 맛이 좋아 부담 없이 목넘김이 좋음</t>
+          <t>고급스러운 선물 포장 — 패키지와 포장이 고급스러워 선물용으로 매우 만족스러움</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>고급스러운 선물 패키지 — 포장이 정성스럽고 패키지가 고급스러워 선물용으로 적합함</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>피로 해소 도움 — 하나씩 섭취 시 피로함이 풀리고 힘이 나는 느낌을 받음</t>
-        </is>
-      </c>
+          <t>우수한 맛과 피로 회복 — 너무 시지 않고 맛이 좋아 목넘김이 편하며 피로 해소 효과가 있음</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>포장 개봉의 불편함 — 개별 비닐이 잘 안 뜯어지고 용기 뚜껑 개봉이 매우 어려움</t>
+          <t>포장 및 용기 개봉 불편 — 비닐 포장이 뜯기 어렵고 캡 용기 버튼이 잘 안 열림</t>
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
@@ -2986,7 +2912,7 @@
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -2994,62 +2920,54 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>'성별 맞춤 설계' 오쏘몰 바이탈 m/f 남성/여성 선택가능 14입 - 시그니처 기프트 에디션 (공식수입)</t>
+          <t>"올인원 명품비타민" 이뮨비타민 올인원 멀티비타민&amp;미네랄 프로 30병</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>59,800원</t>
+          <t>52,900원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/8167919</t>
+          <t>https://gift.kakao.com/product/10903147</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260928090417_28fb45c20b10424fb6c1bd6211e4e4e9.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260928130637_4b5e189e4cc74b40bc33bd3c75d10253.jpg</t>
         </is>
       </c>
       <c r="I9" t="n">
         <v>4</v>
       </c>
       <c r="J9" t="n">
-        <v>776</v>
+        <v>795</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>성별 맞춤 영양 설계 — 남성용과 여성용이 구분되어 영양 성분을 맞춤 섭취 가능함</t>
+          <t>컨디션 개선 및 피로 회복 — 섭취 시 하루 동안 컨디션이 좋아지고 활력이 생김</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>지속적인 피로 개선 — 꾸준히 복용 시 피로감이 줄고 컨디션 유지에 도움이 됨</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>쓴맛 없는 섭취 편의 — 쓴맛이 없으며 개별 포장이라 휴대하고 다니며 복용하기 좋음</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>큰 알약 크기 — 정제 알약의 크기가 다소 커서 한 번에 삼키기가 힘듦</t>
-        </is>
-      </c>
+          <t>편리한 섭취 방식 — 간편하게 복용할 수 있어 일상이나 시험 직전 챙겨 먹기 좋음</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
     </row>
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -3057,51 +2975,51 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>"올인원 명품비타민" 이뮨비타민 올인원 멀티비타민&amp;미네랄 프로 30병</t>
+          <t>'성별 맞춤 설계' 오쏘몰 바이탈 m/f 남성/여성 선택가능 14입 - 시그니처 기프트 에디션 (공식수입)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>닥터블릿</t>
+          <t>오쏘몰</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>52,900원</t>
+          <t>59,800원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/10903147</t>
+          <t>https://gift.kakao.com/product/8167919</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260928130637_4b5e189e4cc74b40bc33bd3c75d10253.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260928090417_28fb45c20b10424fb6c1bd6211e4e4e9.jpg</t>
         </is>
       </c>
       <c r="I10" t="n">
         <v>4</v>
       </c>
       <c r="J10" t="n">
-        <v>795</v>
+        <v>776</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>피로 회복 및 활력 충전 — 섭취 시 하루 동안 활력이 생기고 피로 해소에 도움이 됨</t>
+          <t>성별 맞춤형 옵션 — 남성과 여성용(m/f)을 선택할 수 있어 맞춤 건강 관리가 가능함</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>간편한 복용법 — 하루 한 포씩 간편하게 챙겨 먹기 편함</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>선물용 높은 만족도 — 부모님이나 직장 동료에게 줄 선물용으로 매우 만족스러움</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>지속적인 피로 개선 — 꾸준히 복용 시 활력이 오래 유지되고 피로감이 줄어듦</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>다소 큰 알약 크기 — 기존 제품 대비 알약 크기가 커서 삼키기 부담스러울 수 있음</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
     </row>
@@ -3143,26 +3061,22 @@
         <v>4</v>
       </c>
       <c r="J11" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>피로 감소 및 체력 유지 — 섭취 시 덜 피로하고 일상생활의 체력을 유지하는 데 도움 됨</t>
+          <t>뛰어난 피로 해소 효과 — 복용 시 피로가 줄어들어 매일 챙겨 먹기 적합함</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>옵션 선택과 제형 편의 — 맛 옵션 선택이 가능하며 액상과 캡슐 형태라 마시기 편함</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>정성스러운 선물 패키지 — 선물 패키징이 정성스럽고 합리적인 가격의 대용량 구성임</t>
-        </is>
-      </c>
+          <t>정성스러운 선물 패키징 — 빠른 배송과 정성스러운 포장, 알찬 30일 구성으로 선물 만족도가 높음</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>배송 상자 위생 불량 — 상자에 먼지가 가득 묻어있고 밀봉 스티커가 떨어져 도착함</t>
+          <t>배송 제품의 오염 및 훼손 — 쇼핑백에 먼지가 묻어 있거나 밀봉 스티커가 떼어진 상태로 배송됨</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -3171,7 +3085,7 @@
     <row r="12" ht="38" customHeight="1">
       <c r="B12" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -3179,49 +3093,49 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>"선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
+          <t>리센느 에디션 캡슐레이션 효소 1.8g 2개월분 (5종 중 택1)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>아일로</t>
+          <t>그레인온</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>65,900원</t>
+          <t>24,900원</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/4965835</t>
+          <t>https://gift.kakao.com/product/14208051</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260928091559_44d67bbfbab644e3bc688b7716d83f5d.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261001090325_278bae1c2a364ec2a56a72260f627cdc.jpg</t>
         </is>
       </c>
       <c r="I12" t="n">
         <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>749</v>
+        <v>106</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>화려하고 예쁜 포장 — 선물용 포장이 매우 고급스럽고 예뻐 받는 사람의 기분이 좋아짐</t>
+          <t>우수한 맛과 소화 개선 — 맛이 우수하며 식후 더부룩함과 소화 문제 완화에 도움을 줌</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>맛과 간편한 제형 — 낱개 앰플 형태라 섭취가 간편하며 맛도 부담 없이 마시기 좋음</t>
+          <t>굿즈 및 가성비 구성 — 포토카드와 단백질바 등 증정품 구성과 가성비가 뛰어남</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>비싼 가격대 — 정가 기준 가격대가 비싼 편이라 할인 행사를 이용하게 됨</t>
+          <t>다소 느린 배송 속도 — 제품 수령까지 배송 기간이 다소 오래 걸림</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
@@ -3230,7 +3144,7 @@
     <row r="13" ht="38" customHeight="1">
       <c r="B13" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -3238,51 +3152,51 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장) +파인키위효소+고단백질바 증정</t>
+          <t>"선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>아일로</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>43,900원</t>
+          <t>65,900원</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13180343</t>
+          <t>https://gift.kakao.com/product/4965835</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260923111828_e9badd52c1a54899b5226c1eae768639.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260928091559_44d67bbfbab644e3bc688b7716d83f5d.jpg</t>
         </is>
       </c>
       <c r="I13" t="n">
         <v>4</v>
       </c>
       <c r="J13" t="n">
-        <v>1682</v>
+        <v>749</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>속 편한 소화 개선 — 식후 섭취 시 소화를 돕고 속을 편안하게 유지해줌</t>
+          <t>화려하고 고급스러운 포장 — 포장이 매우 고급스럽고 예뻐 선물용으로 만족도가 높음</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>구수한 고구마 맛 — 고소하고 구수한 고구마 맛이 나 거부감 없이 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>착한 가격과 증정 혜택 — 가격이 저렴하고 단백질바 등 증정 사은품 만족도가 높음</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>맛과 간편한 개별 섭취 — 맛이 좋고 앰플 타입으로 낱개 섭취가 간편함</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>부담스러운 가격대 — 가격이 다소 높게 책정되어 할인 기간에 구매하게 됨</t>
+        </is>
+      </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
     </row>
@@ -3297,60 +3211,52 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>[한끼통살] 닭가슴살 한달 식단 패키지 30팩+(증정)보냉백</t>
+          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장) +파인키위효소+고단백질바 증정</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>한끼통살</t>
+          <t>그레인온</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>45,800원</t>
+          <t>43,900원</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/11566779</t>
+          <t>https://gift.kakao.com/product/13180343</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260429112212_3e1db89ad7174b6989286381ae7257c6.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260923111828_e9badd52c1a54899b5226c1eae768639.jpg</t>
         </is>
       </c>
       <c r="I14" t="n">
         <v>4</v>
       </c>
       <c r="J14" t="n">
-        <v>152</v>
+        <v>1682</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>뛰어난 포만감과 맛 — 한 개만 먹어도 포만감이 크며 소스가 맛이 있어 다이어트에 좋음</t>
+          <t>구수한 고구마 맛 — 구수한 고구마 맛이 나 거부감 없이 맛있게 먹을 수 있음</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>다채로운 상품 구성 — 30팩에 달하는 다양한 종류로 구성되어 골라 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>가성비와 빠른 배송 — 할인가 구매 시 가성비가 훌륭하며 배송 속도가 빠름</t>
-        </is>
-      </c>
+          <t>소화 촉진 및 속 편안함 — 식후 속을 편안하게 해주고 배변 활동 완화에 도움을 줌</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>구성품 오배송 및 누락 — 주문한 상품 종류가 누락되거나 중복 오배송되는 경우가 발생함</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>포장 터짐 및 소스 누출 — 진공 포장이 헐겁거나 배송 중 팩이 터져 소스가 새어 나옴</t>
-        </is>
-      </c>
+          <t>증정품의 작은 크기 — 함께 제공되는 증정용 단백질 칩의 크기가 다소 작음</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
     </row>
     <row r="15" ht="38" customHeight="1">
@@ -3364,7 +3270,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>[한끼통살] 단백질 든든형 닭가슴살 21일식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
+          <t>[한끼통살] 닭가슴살 한달 식단 패키지 30팩+(증정)보냉백</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -3374,46 +3280,46 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>33,900원</t>
+          <t>45,800원</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12860133</t>
+          <t>https://gift.kakao.com/product/11566779</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260821134612_62bbe99621d6408d9e7e793b67d6e079.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260429112212_3e1db89ad7174b6989286381ae7257c6.jpg</t>
         </is>
       </c>
       <c r="I15" t="n">
         <v>4</v>
       </c>
       <c r="J15" t="n">
-        <v>59</v>
+        <v>152</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>부드러운 식감과 맛 — 퍽퍽하지 않고 부드러우며 잡내 없이 완벽한 소스 맛을 자랑함</t>
+          <t>뛰어난 맛과 높은 포만감 — 맛이 아주 우수하며 한 개만 먹어도 포만감이 오래 유지됨</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>다양한 종류와 구성 — 스테이크, 주먹밥 등 다양한 구성이라 다이어트 시 질리지 않음</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>훌륭한 가성비 — 할인 행사 구매 시 매우 저렴한 가격에 넉넉하게 쟁여둘 수 있음</t>
-        </is>
-      </c>
+          <t>다양한 종류 구성 — 여러 맛의 제품이 골고루 구성되어 질리지 않고 먹기 좋음</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>선호 품목 구성 제외 — 가장 맛있는 특정 파우치형 제품이 포함되어 있지 않아 아쉬움</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr"/>
+          <t>배송 누락 및 오배송 — 주문한 구성과 다르게 다른 제품이 중복 배송되거나 누락됨</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>제품 팩 터짐 및 포장 불량 — 진공 포장이 헐렁하거나 팩이 터져 소스가 새어 나오는 현상이 있음</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr"/>
     </row>
     <row r="16" ht="38" customHeight="1">
@@ -3427,58 +3333,58 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나 택1</t>
+          <t>[한끼통살] 단백질 든든형 닭가슴살 21일식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>셀렉스</t>
+          <t>한끼통살</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>28,900원</t>
+          <t>33,900원</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13550266</t>
+          <t>https://gift.kakao.com/product/12860133</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260907094509_48a662610e174029823081c612ed4755.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260821134612_62bbe99621d6408d9e7e793b67d6e079.jpg</t>
         </is>
       </c>
       <c r="I16" t="n">
         <v>4</v>
       </c>
       <c r="J16" t="n">
-        <v>216</v>
+        <v>59</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>비리지 않고 달콤한 맛 — 단백질 음료 특유의 비린 맛 없이 진하고 달달하게 마시기 좋음</t>
+          <t>부드럽고 잡내 없는 맛 — 닭가슴살이 퍽퍽하지 않고 부드러우며 잡내 없이 맛있음</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>운동 후 영양 및 포만감 — 운동 후 마시면 허기짐을 채워주고 영양을 충전하기 적합함</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>슬림한 휴대용 용기 — 패키지가 슬림하여 가방에 넣고 다니며 챙겨 먹기 간편함</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>다양한 구성과 가성비 — 다양한 종류를 저렴한 가격에 구매할 수 있어 가성비가 높음</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>특정 선호 품목의 부재 — 파우치형 그릴 제품 등 일부 선호하는 종류가 구성에 없어 아쉬움</t>
+        </is>
+      </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
     </row>
     <row r="17" ht="38" customHeight="1">
       <c r="B17" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -3486,55 +3392,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>리센느 에디션 캡슐레이션 효소 1.8g 2개월분 (5종 중 택1)</t>
+          <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나 택1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>셀렉스</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>24,900원</t>
+          <t>28,900원</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/14208051</t>
+          <t>https://gift.kakao.com/product/13550266</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261001090325_278bae1c2a364ec2a56a72260f627cdc.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260907094509_48a662610e174029823081c612ed4755.jpg</t>
         </is>
       </c>
       <c r="I17" t="n">
         <v>4</v>
       </c>
       <c r="J17" t="n">
-        <v>106</v>
+        <v>216</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>식후 더부룩함 완화 — 식사 후 섭취 시 속 더부룩함이 줄어들고 속이 편안해짐</t>
+          <t>비린 맛 없는 달콤함 — 단백질 특유의 비린 맛이나 텁텁함이 없고 달콤하여 마시기 편함</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>기호성 높은 맛 — 베리말차 등 기호성 우수한 맛이라 맛있게 먹을 수 있음</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>푸짐한 구성품 증정 — 포토카드 및 단백질바 등 증정품 구성이 알차고 가성비가 좋음</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>배송 지연 — 주문 후 받아보기까지 배송 기간이 조금 늦은 편임</t>
-        </is>
-      </c>
+          <t>슬림한 용기의 휴대성 — 패키지가 슬림하여 가방에 넣고 다니며 간편하게 섭취 가능함</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
     </row>
@@ -3580,22 +3478,18 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>부드럽고 촉촉한 식감 — 퍽퍽하지 않고 촉촉하며 한입 볼 제형이라 먹기 편함</t>
+          <t>촉촉하고 쫄깃한 식감 — 퍽퍽하지 않고 촉촉하며 간이 적당해 맛있게 단백질을 채울 수 있음</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>맛있는 간과 소스 — 간이 알맞고 맛이 다양하여 부담 없이 맛있게 먹을 수 있음</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>간편한 조리 방법 — 전자레인지에 간단히 데우기만 하면 되어 식사 준비가 편리함</t>
-        </is>
-      </c>
+          <t>전자레인지 조리 간편성 — 전자레인지에 간단히 데워 먹을 수 있어 식사 준비가 매우 편리함</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>다소 느린 배송 — 주문 후 상품 배송에 시간이 다소 소요됨</t>
+          <t>다소 느린 배송 — 주문 후 제품 수령까지 배송 시간이 다소 걸림</t>
         </is>
       </c>
       <c r="O18" t="inlineStr"/>
@@ -3604,7 +3498,7 @@
     <row r="19" ht="38" customHeight="1">
       <c r="B19" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -3612,58 +3506,62 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
+          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>알디콤</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>43,900원</t>
+          <t>33,200원</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/7417420</t>
+          <t>https://gift.kakao.com/product/12064702</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260706153340_3e124da6e254462d9a7efad2521e3b9e.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260827134326_6543fa160cfd4c4294103fd47b3d0a12.jpg</t>
         </is>
       </c>
       <c r="I19" t="n">
         <v>4</v>
       </c>
       <c r="J19" t="n">
-        <v>248</v>
+        <v>20</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>고함량 체력 증진 — 6,200mg 고함량이라 운동 전후 체력 유지와 피로 회복에 탁월함</t>
+          <t>확실한 숙취 해소 효과 — 음주 전후 복용 시 다음 날 숙취와 몸의 무거움이 확실히 덜함</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>개별 스틱 간편 복용 — 하루 한 포 스틱 형태로 휴대가 용이하며 복용이 편리함</t>
+          <t>스틱형 휴대 및 복용 편의 — 스틱 포장으로 휴대하기 좋고 물 없이 바로 먹을 수 있음</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>고급 선물 세트 포장 — 쇼핑백과 추가 스틱이 함께 제공되어 선물용으로 매우 우수함</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>고급스러운 선물세트 구성 — 보라색 스틱과 쇼핑백 패키지가 고급스러워 선물용으로 적합함</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>한약 특유의 씁쓸한 맛 — 약재 성분으로 인해 씁쓸한 한약 맛이 느껴질 수 있음</t>
+        </is>
+      </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
     </row>
     <row r="20" ht="38" customHeight="1">
       <c r="B20" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -3671,50 +3569,46 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
+          <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>알디콤</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>33,200원</t>
+          <t>43,900원</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12064702</t>
+          <t>https://gift.kakao.com/product/7417420</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260827134326_6543fa160cfd4c4294103fd47b3d0a12.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260706153340_3e124da6e254462d9a7efad2521e3b9e.jpg</t>
         </is>
       </c>
       <c r="I20" t="n">
         <v>4</v>
       </c>
       <c r="J20" t="n">
-        <v>19</v>
+        <v>248</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>확실한 숙취 완화 — 음주 전후 복용 시 다음 날 숙취와 몸의 무거움이 확연히 줄어듦</t>
+          <t>고함량으로 인한 활력 증진 — 6200mg 고함량 아르기닌으로 운동 시 지구력 및 일상 활력 증진에 효과적임</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>고급스러운 패키지 — 보라색 리본 손잡이 및 전용 쇼핑백으로 구성되어 선물하기 좋음</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>물 없이 간편 섭취 — 스틱 액상 제형이라 물 없이도 장소 제약 없이 간편하게 복용 가능함</t>
-        </is>
-      </c>
+          <t>간편한 하루 1포 섭취 — 하루 한 포 개별 포장으로 휴대가 쉽고 챙겨 먹기 간편함</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
@@ -3761,19 +3655,15 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>속 편한 소화 효능 — 섭취 후 소화가 원활하고 속이 편안해지는 느낌을 받음</t>
+          <t>합리적인 가격과 사은품 — 저렴한 가격에 증정품 과자까지 구성되어 가성비가 훌륭함</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>푸짐한 사은품 증정 — 저당씬칩 등 맛있는 과자 증정품이 푸짐하게 도착함</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>저렴한 구매 가격 — 할인된 저렴한 가격으로 많은 양을 알차게 구매함</t>
-        </is>
-      </c>
+          <t>우수한 맛과 속 편안함 — 맛이 좋고 복용 후 속이 편안해짐을 느낌</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
@@ -3924,12 +3814,12 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>멀티비타민/종합비타민</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -3981,12 +3871,12 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>닥터블릿</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
           <t>오쏘몰</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>닥터블릿</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -4038,12 +3928,12 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>"올인원 명품비타민" 이뮨비타민 올인원 멀티비타민&amp;미네랄 프로 30병</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
           <t>'성별 맞춤 설계' 오쏘몰 바이탈 m/f 남성/여성 선택가능 14입 - 시그니처 기프트 에디션 (공식수입)</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>"올인원 명품비타민" 이뮨비타민 올인원 멀티비타민&amp;미네랄 프로 30병</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -4096,16 +3986,16 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>16172</v>
+        <v>16173</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>15506</v>
+        <v>15507</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>3379</v>
+        <v>3381</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>6489</v>
+        <v>6490</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>803</v>
@@ -4114,19 +4004,19 @@
         <v>8737</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1713</v>
+        <v>1715</v>
       </c>
       <c r="J7" s="3" t="n">
+        <v>795</v>
+      </c>
+      <c r="K7" s="3" t="n">
         <v>776</v>
       </c>
-      <c r="K7" s="3" t="n">
-        <v>795</v>
-      </c>
       <c r="L7" s="3" t="n">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="8" ht="90" customHeight="1">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
@@ -4134,74 +4024,66 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>간편한 복용 방법 — 하루 한 번 액상과 정제를 함께 먹는 제형이라 간편함
-피로 회복 기대감 — 피로나 기력 저하 시 섭취하여 건강 관리에 도움이 됨</t>
+          <t>피로 회복 및 체력 증진 — 섭취 후 피로감이 줄어들고 기력 및 면역력 향상에 도움을 줌
+간편한 복용 방식 — 하루 한 번 액상과 정제를 함께 먹는 형태로 복용이 매우 간편함</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>휴대 및 복용 편의 — 물 없이 가지고 다니며 피곤할 때 간편하게 먹기 좋음
-맛과 풍미 만족 — 맛이 좋아 거부감 없이 맛있게 섭취가 가능함
-빠르고 꼼꼼한 배송 — 배송이 빠르며 포장이 꼼꼼하게 처리되어 도착함</t>
+          <t>체력 증진 및 피로 회복 — 수면 효율이 좋아지고 피로 회복과 체력 개선 효과가 뛰어남
+좋은 맛과 휴대 편의성 — 맛이 좋고 물 없이 챙겨 먹을 수 있어 휴대 및 복용이 용이함</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>선물용으로 적합 — 깔끔한 구성과 패키지로 명절이나 위로 선물로 좋음
-활력 증진 도움 — 먹기 편하며 섭취 후 기운이 나는 느낌을 받음</t>
+          <t>선물용으로 높은 만족도 — 패키지가 깔끔하고 브랜드 인지도가 높아 선물용으로 적합함
+피로 회복 및 활력 증진 — 섭취 시 피로 해소에 도움을 주고 섭취 방법이 편리함</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>젤리 제형의 편의성 — 구미 젤리 형태로 물 없이 간편하게 섭취 가능함
-맛있는 맛과 식감 — 영양제 특유의 거부감 없이 젤리처럼 맛있게 먹기 좋음
-귀여운 선물 패키지 — 포장이 깔끔하고 귀여워 가볍게 선물하기에 적합함</t>
+          <t>맛있는 구미 제형 — 마이구미처럼 맛이 좋아 거부감 없이 섭취할 수 있음
+간편한 섭취 방식 — 알약을 못 먹는 사람도 물 없이 간편하게 챙겨 먹을 수 있음</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>피로 회복 및 체력 관리 — 섭취 후 하루 종일 지치지 않고 기운을 차리는 데 도움 됨
-고급스러운 포장 — 패키지가 예쁘고 정성스럽게 포장되어 선물용으로 훌륭함
-합리적인 가격과 배송 — 저렴한 가격에 빠른 배송으로 받아서 만족함</t>
+          <t>신속한 피로 회복 — 체력 방전이나 피로감이 심할 때 빠르게 기운을 차리는 데 도움을 줌
+예쁜 선물 패키지 — 패키지 구성이 예뻐서 선물로 받았을 때 기분이 좋아짐</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>알찬 구성과 깔끔한 포장 — 증정품이 더해진 구성에 깔끔한 패키지라 선물하기 좋음
-기력 및 피로 회복 — 지치고 피곤할 때 간편히 챙겨 먹으며 기운을 얻음
-올인원 간편 섭취 — 여러 영양제를 따로 챙길 필요 없이 한 번에 복용 가능함</t>
+          <t>깔끔한 패키지 구성 — 단독 에디션 패키지가 깔끔하고 추가 증정 구성이 알참
+기력 회복 및 간편성 — 지치고 피곤할 때 간편하게 챙겨 먹기 좋음</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>목넘김과 기호성 — 과하게 시지 않고 맛이 좋아 부담 없이 목넘김이 좋음
-고급스러운 선물 패키지 — 포장이 정성스럽고 패키지가 고급스러워 선물용으로 적합함
-피로 해소 도움 — 하나씩 섭취 시 피로함이 풀리고 힘이 나는 느낌을 받음</t>
+          <t>고급스러운 선물 포장 — 패키지와 포장이 고급스러워 선물용으로 매우 만족스러움
+우수한 맛과 피로 회복 — 너무 시지 않고 맛이 좋아 목넘김이 편하며 피로 해소 효과가 있음</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>성별 맞춤 영양 설계 — 남성용과 여성용이 구분되어 영양 성분을 맞춤 섭취 가능함
-지속적인 피로 개선 — 꾸준히 복용 시 피로감이 줄고 컨디션 유지에 도움이 됨
-쓴맛 없는 섭취 편의 — 쓴맛이 없으며 개별 포장이라 휴대하고 다니며 복용하기 좋음</t>
+          <t>컨디션 개선 및 피로 회복 — 섭취 시 하루 동안 컨디션이 좋아지고 활력이 생김
+편리한 섭취 방식 — 간편하게 복용할 수 있어 일상이나 시험 직전 챙겨 먹기 좋음</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>피로 회복 및 활력 충전 — 섭취 시 하루 동안 활력이 생기고 피로 해소에 도움이 됨
-간편한 복용법 — 하루 한 포씩 간편하게 챙겨 먹기 편함
-선물용 높은 만족도 — 부모님이나 직장 동료에게 줄 선물용으로 매우 만족스러움</t>
+          <t>성별 맞춤형 옵션 — 남성과 여성용(m/f)을 선택할 수 있어 맞춤 건강 관리가 가능함
+지속적인 피로 개선 — 꾸준히 복용 시 활력이 오래 유지되고 피로감이 줄어듦</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>피로 감소 및 체력 유지 — 섭취 시 덜 피로하고 일상생활의 체력을 유지하는 데 도움 됨
-옵션 선택과 제형 편의 — 맛 옵션 선택이 가능하며 액상과 캡슐 형태라 마시기 편함
-정성스러운 선물 패키지 — 선물 패키징이 정성스럽고 합리적인 가격의 대용량 구성임</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1">
+          <t>뛰어난 피로 해소 효과 — 복용 시 피로가 줄어들어 매일 챙겨 먹기 적합함
+정성스러운 선물 패키징 — 빠른 배송과 정성스러운 포장, 알찬 30일 구성으로 선물 만족도가 높음</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
@@ -4209,18 +4091,17 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>용기 파손 발생 — 배송이나 이동 중 일부 제품 용기가 폭파 및 파손됨
-단기 효과 미흡 — 가끔 먹는 단기 섭취 시 눈에 띄는 빠른 효과를 느끼기 어려움</t>
+          <t>제품 터짐 및 용기 하자 — 보관이나 이동 중 일부 용기가 폭발하듯 깨져 내용물이 새어나옴</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>공복 섭취 시 속 불편 — 빈속에 복용 시 울렁거림이나 구토 증상이 나타날 수 있음</t>
+          <t>공복 섭취 시 속 불편함 — 빈속에 복용 시 강한 속 울렁거림이나 구토 증상이 발생할 수 있음</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>완충재 부족 배송 — 완충제 없이 배송되어 제품 박스가 찌그러져 도착함</t>
+          <t>부실한 완충 포장 — 완충재 없이 포장되어 배송 중 상자가 찌그러져 도착함</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr"/>
@@ -4228,18 +4109,18 @@
       <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>포장 개봉의 불편함 — 개별 비닐이 잘 안 뜯어지고 용기 뚜껑 개봉이 매우 어려움</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>큰 알약 크기 — 정제 알약의 크기가 다소 커서 한 번에 삼키기가 힘듦</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr"/>
+          <t>포장 및 용기 개봉 불편 — 비닐 포장이 뜯기 어렵고 캡 용기 버튼이 잘 안 열림</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>다소 큰 알약 크기 — 기존 제품 대비 알약 크기가 커서 삼키기 부담스러울 수 있음</t>
+        </is>
+      </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>배송 상자 위생 불량 — 상자에 먼지가 가득 묻어있고 밀봉 스티커가 떨어져 도착함</t>
+          <t>배송 제품의 오염 및 훼손 — 쇼핑백에 먼지가 묻어 있거나 밀봉 스티커가 떼어진 상태로 배송됨</t>
         </is>
       </c>
     </row>
@@ -4286,12 +4167,12 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>52,900원</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
           <t>59,800원</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>52,900원</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -4439,47 +4320,47 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
           <t>피부/미용</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="K15" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -4496,34 +4377,34 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
+          <t>그레인온</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
           <t>아일로</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>그레인온</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>한끼통살</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>한끼통살</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>셀렉스</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>그레인온</t>
-        </is>
-      </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
           <t>한끼통살</t>
@@ -4531,12 +4412,12 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>알디콤</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
           <t>익스트림</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>알디콤</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -4553,34 +4434,34 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
+          <t>리센느 에디션 캡슐레이션 효소 1.8g 2개월분 (5종 중 택1)</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
           <t>"선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장) +파인키위효소+고단백질바 증정</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>[한끼통살] 닭가슴살 한달 식단 패키지 30팩+(증정)보냉백</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>[한끼통살] 단백질 든든형 닭가슴살 21일식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나 택1</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>리센느 에디션 캡슐레이션 효소 1.8g 2개월분 (5종 중 택1)</t>
-        </is>
-      </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
           <t>[한끼통살] 닭가슴살 순삭 10팩세트(소스통살5+닭가슴살볼5)</t>
@@ -4588,12 +4469,12 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
           <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -4646,31 +4527,31 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
+        <v>106</v>
+      </c>
+      <c r="D19" s="3" t="n">
         <v>749</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="E19" s="3" t="n">
         <v>1682</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="F19" s="3" t="n">
         <v>152</v>
       </c>
-      <c r="F19" s="3" t="n">
+      <c r="G19" s="3" t="n">
         <v>59</v>
       </c>
-      <c r="G19" s="3" t="n">
+      <c r="H19" s="3" t="n">
         <v>216</v>
-      </c>
-      <c r="H19" s="3" t="n">
-        <v>106</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>69</v>
       </c>
       <c r="J19" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="K19" s="3" t="n">
         <v>248</v>
-      </c>
-      <c r="K19" s="3" t="n">
-        <v>19</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>901</v>
@@ -4684,71 +4565,63 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>화려하고 예쁜 포장 — 선물용 포장이 매우 고급스럽고 예뻐 받는 사람의 기분이 좋아짐
-맛과 간편한 제형 — 낱개 앰플 형태라 섭취가 간편하며 맛도 부담 없이 마시기 좋음</t>
+          <t>우수한 맛과 소화 개선 — 맛이 우수하며 식후 더부룩함과 소화 문제 완화에 도움을 줌
+굿즈 및 가성비 구성 — 포토카드와 단백질바 등 증정품 구성과 가성비가 뛰어남</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>속 편한 소화 개선 — 식후 섭취 시 소화를 돕고 속을 편안하게 유지해줌
-구수한 고구마 맛 — 고소하고 구수한 고구마 맛이 나 거부감 없이 먹기 좋음
-착한 가격과 증정 혜택 — 가격이 저렴하고 단백질바 등 증정 사은품 만족도가 높음</t>
+          <t>화려하고 고급스러운 포장 — 포장이 매우 고급스럽고 예뻐 선물용으로 만족도가 높음
+맛과 간편한 개별 섭취 — 맛이 좋고 앰플 타입으로 낱개 섭취가 간편함</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>뛰어난 포만감과 맛 — 한 개만 먹어도 포만감이 크며 소스가 맛이 있어 다이어트에 좋음
-다채로운 상품 구성 — 30팩에 달하는 다양한 종류로 구성되어 골라 먹기 좋음
-가성비와 빠른 배송 — 할인가 구매 시 가성비가 훌륭하며 배송 속도가 빠름</t>
+          <t>구수한 고구마 맛 — 구수한 고구마 맛이 나 거부감 없이 맛있게 먹을 수 있음
+소화 촉진 및 속 편안함 — 식후 속을 편안하게 해주고 배변 활동 완화에 도움을 줌</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>부드러운 식감과 맛 — 퍽퍽하지 않고 부드러우며 잡내 없이 완벽한 소스 맛을 자랑함
-다양한 종류와 구성 — 스테이크, 주먹밥 등 다양한 구성이라 다이어트 시 질리지 않음
-훌륭한 가성비 — 할인 행사 구매 시 매우 저렴한 가격에 넉넉하게 쟁여둘 수 있음</t>
+          <t>뛰어난 맛과 높은 포만감 — 맛이 아주 우수하며 한 개만 먹어도 포만감이 오래 유지됨
+다양한 종류 구성 — 여러 맛의 제품이 골고루 구성되어 질리지 않고 먹기 좋음</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>비리지 않고 달콤한 맛 — 단백질 음료 특유의 비린 맛 없이 진하고 달달하게 마시기 좋음
-운동 후 영양 및 포만감 — 운동 후 마시면 허기짐을 채워주고 영양을 충전하기 적합함
-슬림한 휴대용 용기 — 패키지가 슬림하여 가방에 넣고 다니며 챙겨 먹기 간편함</t>
+          <t>부드럽고 잡내 없는 맛 — 닭가슴살이 퍽퍽하지 않고 부드러우며 잡내 없이 맛있음
+다양한 구성과 가성비 — 다양한 종류를 저렴한 가격에 구매할 수 있어 가성비가 높음</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>식후 더부룩함 완화 — 식사 후 섭취 시 속 더부룩함이 줄어들고 속이 편안해짐
-기호성 높은 맛 — 베리말차 등 기호성 우수한 맛이라 맛있게 먹을 수 있음
-푸짐한 구성품 증정 — 포토카드 및 단백질바 등 증정품 구성이 알차고 가성비가 좋음</t>
+          <t>비린 맛 없는 달콤함 — 단백질 특유의 비린 맛이나 텁텁함이 없고 달콤하여 마시기 편함
+슬림한 용기의 휴대성 — 패키지가 슬림하여 가방에 넣고 다니며 간편하게 섭취 가능함</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>부드럽고 촉촉한 식감 — 퍽퍽하지 않고 촉촉하며 한입 볼 제형이라 먹기 편함
-맛있는 간과 소스 — 간이 알맞고 맛이 다양하여 부담 없이 맛있게 먹을 수 있음
-간편한 조리 방법 — 전자레인지에 간단히 데우기만 하면 되어 식사 준비가 편리함</t>
+          <t>촉촉하고 쫄깃한 식감 — 퍽퍽하지 않고 촉촉하며 간이 적당해 맛있게 단백질을 채울 수 있음
+전자레인지 조리 간편성 — 전자레인지에 간단히 데워 먹을 수 있어 식사 준비가 매우 편리함</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>고함량 체력 증진 — 6,200mg 고함량이라 운동 전후 체력 유지와 피로 회복에 탁월함
-개별 스틱 간편 복용 — 하루 한 포 스틱 형태로 휴대가 용이하며 복용이 편리함
-고급 선물 세트 포장 — 쇼핑백과 추가 스틱이 함께 제공되어 선물용으로 매우 우수함</t>
+          <t>확실한 숙취 해소 효과 — 음주 전후 복용 시 다음 날 숙취와 몸의 무거움이 확실히 덜함
+스틱형 휴대 및 복용 편의 — 스틱 포장으로 휴대하기 좋고 물 없이 바로 먹을 수 있음
+고급스러운 선물세트 구성 — 보라색 스틱과 쇼핑백 패키지가 고급스러워 선물용으로 적합함</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>확실한 숙취 완화 — 음주 전후 복용 시 다음 날 숙취와 몸의 무거움이 확연히 줄어듦
-고급스러운 패키지 — 보라색 리본 손잡이 및 전용 쇼핑백으로 구성되어 선물하기 좋음
-물 없이 간편 섭취 — 스틱 액상 제형이라 물 없이도 장소 제약 없이 간편하게 복용 가능함</t>
+          <t>고함량으로 인한 활력 증진 — 6200mg 고함량 아르기닌으로 운동 시 지구력 및 일상 활력 증진에 효과적임
+간편한 하루 1포 섭취 — 하루 한 포 개별 포장으로 휴대가 쉽고 챙겨 먹기 간편함</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>속 편한 소화 효능 — 섭취 후 소화가 원활하고 속이 편안해지는 느낌을 받음
-푸짐한 사은품 증정 — 저당씬칩 등 맛있는 과자 증정품이 푸짐하게 도착함
-저렴한 구매 가격 — 할인된 저렴한 가격으로 많은 양을 알차게 구매함</t>
+          <t>합리적인 가격과 사은품 — 저렴한 가격에 증정품 과자까지 구성되어 가성비가 훌륭함
+우수한 맛과 속 편안함 — 맛이 좋고 복용 후 속이 편안해짐을 느낌</t>
         </is>
       </c>
     </row>
@@ -4760,33 +4633,41 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>비싼 가격대 — 정가 기준 가격대가 비싼 편이라 할인 행사를 이용하게 됨</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr"/>
+          <t>다소 느린 배송 속도 — 제품 수령까지 배송 기간이 다소 오래 걸림</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>부담스러운 가격대 — 가격이 다소 높게 책정되어 할인 기간에 구매하게 됨</t>
+        </is>
+      </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>구성품 오배송 및 누락 — 주문한 상품 종류가 누락되거나 중복 오배송되는 경우가 발생함
-포장 터짐 및 소스 누출 — 진공 포장이 헐겁거나 배송 중 팩이 터져 소스가 새어 나옴</t>
+          <t>증정품의 작은 크기 — 함께 제공되는 증정용 단백질 칩의 크기가 다소 작음</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>선호 품목 구성 제외 — 가장 맛있는 특정 파우치형 제품이 포함되어 있지 않아 아쉬움</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>배송 지연 — 주문 후 받아보기까지 배송 기간이 조금 늦은 편임</t>
-        </is>
-      </c>
+          <t>배송 누락 및 오배송 — 주문한 구성과 다르게 다른 제품이 중복 배송되거나 누락됨
+제품 팩 터짐 및 포장 불량 — 진공 포장이 헐렁하거나 팩이 터져 소스가 새어 나오는 현상이 있음</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>특정 선호 품목의 부재 — 파우치형 그릴 제품 등 일부 선호하는 종류가 구성에 없어 아쉬움</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr"/>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>다소 느린 배송 — 주문 후 상품 배송에 시간이 다소 소요됨</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="inlineStr"/>
+          <t>다소 느린 배송 — 주문 후 제품 수령까지 배송 시간이 다소 걸림</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>한약 특유의 씁쓸한 맛 — 약재 성분으로 인해 씁쓸한 한약 맛이 느껴질 수 있음</t>
+        </is>
+      </c>
       <c r="K21" s="3" t="inlineStr"/>
       <c r="L21" s="3" t="inlineStr"/>
     </row>
@@ -4798,34 +4679,34 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
+          <t>24,900원</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
           <t>65,900원</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>43,900원</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>45,800원</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>33,900원</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>28,900원</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>24,900원</t>
-        </is>
-      </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
           <t>20,900원</t>
@@ -4833,12 +4714,12 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>33,200원</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
           <t>43,900원</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>33,200원</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
@@ -5033,7 +4914,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -5041,58 +4922,54 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>종근당 데일리와이즈 포스트바이오틱스 구미 7일분</t>
+          <t>[김종국 PICK] 익스트림 아르기닌 에너지온 2개입 2일분</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>종근당</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1,000원</t>
+          <t>1,500원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032306207&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=987253277&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260417/EkCI0eksQMTFgi7Ae5eM032306207_00_01EkCI0eksQMTFgi7Ae5eM.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260422/eIhoZ9JSC5jbp33vSbZX987253277_00_01eIhoZ9JSC5jbp33vSbZX.jpg</t>
         </is>
       </c>
       <c r="I2" t="n">
         <v>4.8</v>
       </c>
       <c r="J2" t="n">
-        <v>341</v>
+        <v>805</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>맛있는 요구르트 맛 — 요구르트 맛이 나서 질리지 않고 맛있게 먹을 수 있음</t>
+          <t>뛰어난 가성비 — 가격이 저렴하여 부담 없이 구매하기 좋음</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>건강한 간식 대용 — 몸에 해로운 일반 과자 대신 건강하게 간식으로 먹기 좋음</t>
+          <t>높은 재구매 만족도 — 제품 품질에 만족하여 지속적으로 재주문함</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>적은 제품 용량 — 용량이 다소 적어서 빠르게 소비하게 됨</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
     </row>
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -5100,12 +4977,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>동화 바이마그랩 마그네슘 식이섬유 5포 5일분</t>
+          <t>[다영 PICK] 셀트리온 브로멜라인＆알파 CD 30정 15일분</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>동화약품</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -5115,34 +4992,30 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601618642&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=025575127&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260406/wJCESiflDyulw8oZ8pW1601618642_00_00wJCESiflDyulw8oZ8pW1.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260605/VsX5iaJon2xHHTs8AQHv025575127_00_01VsX5iaJon2xHHTs8AQHv.jpg</t>
         </is>
       </c>
       <c r="I3" t="n">
         <v>4.7</v>
       </c>
       <c r="J3" t="n">
-        <v>514</v>
+        <v>903</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>우수한 가성비 — 가격이 매우 저렴하여 매일 부담 없이 복용 가능함</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>피로 회복 기대 — 마그네슘 성분 덕에 피로 회복에 어느 정도 도움이 됨</t>
-        </is>
-      </c>
+          <t>편리한 복용성 — 알약 형태라 먹기 편하고 체중 관리에 도움을 줌</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>변비 개선 미흡 — 피로 회복과 달리 변비 관련 효과는 크게 느끼기 어려움</t>
+          <t>아쉬운 재구매 의사 — 특별한 체감 효과가 부족하여 재구매로 이어지지 않음</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
@@ -5151,7 +5024,7 @@
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -5159,49 +5032,49 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>동국 맛있는 샐러드 미니볼 비타 15포 15일분</t>
+          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910967&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=944863413&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260415/rKimZ2TE65XK1Rwibsnv610910967_00_02rKimZ2TE65XK1Rwibsnv.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260605/8ADhx4mYwiTujsVcCSTD944863413_00_018ADhx4mYwiTujsVcCSTD.jpg</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J4" t="n">
-        <v>1519</v>
+        <v>2712</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>간편한 간식 대용 — 맛있고 간편해서 허기질 때나 출출할 때 먹기 좋음</t>
+          <t>부담 없는 커피 맛 — 카페인 부담이 적고 진한 커피 맛이 나 커피 대체용으로 좋음</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>합리적인 가성비 — 저렴한 가격 덕분에 아이들 간식용으로 재구매하기 좋음</t>
+          <t>변비 개선 보조 — 꾸준히 마실 경우 변비 해소에 도움을 줌</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>단단한 제형 식감 — 제형이 다소 딱딱하여 씹어 먹을 때 불편함이 있음</t>
+          <t>잦은 제품 품절 — 구매하려 할 때 품절인 경우가 많아 재구매가 어려움</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
@@ -5210,7 +5083,7 @@
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -5218,12 +5091,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[홍삼매니아] 자연관 홍삼정 에너타임 10포 10일분</t>
+          <t>[우형재 PICK] 익스트림 모노크레아틴 플러스 120 g 40일분</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>자연관</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -5233,35 +5106,31 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=901762097&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=987253276&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250807/jJGIxkBNqg0FzVjNiyoV901762097_00_01jJGIxkBNqg0FzVjNiyoV.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260422/qm625V7JKEa8Iu7GrFAf987253276_00_01qm625V7JKEa8Iu7GrFAf.jpg</t>
         </is>
       </c>
       <c r="I5" t="n">
         <v>4.8</v>
       </c>
       <c r="J5" t="n">
-        <v>1103</v>
+        <v>714</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>활력 증진 체감 — 섭취 후 피로가 풀리고 몸의 활력이 느껴져 만족함</t>
+          <t>압도적인 가성비 — 타 플랫폼 제품 대비 가격 경쟁력이 매우 뛰어남</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>뛰어난 가성비 — 저렴한 가격임에도 홍삼 제품 본연의 기능에 충실함</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>간편한 섭취 방식 — 스틱 형태로 어디서나 가볍게 섭취하기 편리함</t>
-        </is>
-      </c>
+          <t>간편한 섭취 방식 — 계량 스쿱 등으로 간편하게 떠먹기 편리함</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
@@ -5277,12 +5146,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>락피도 티니핑 면역스틱 12포 12일분</t>
+          <t>오브맘 활력에너지B 하루구미 30일분</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>락피도</t>
+          <t>오브맘</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -5292,36 +5161,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=951817117&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602132&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260226/IXAU5YWeB9Z3g8kwCzhg951817117_00_01IXAU5YWeB9Z3g8kwCzhg.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250922/FWBWePRv27KbgtvBHof6613602132_00_01FWBWePRv27KbgtvBHof6.jpg</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J6" t="n">
-        <v>654</v>
+        <v>756</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>아이들의 높은 선호도 — 기호성이 높아 아이들이 거부감 없이 먼저 찾아 먹음</t>
+          <t>맛있는 구미 제형 — 약 같은 맛 없이 맛있는 젤리 형태로 즐길 수 있음</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>맛있는 젤리 제형 — 망고맛 젤리 형태라 간식처럼 즐겁게 먹일 수 있음</t>
+          <t>간편한 영양 챙김 — 구미 타입이라 거부감 없이 간편하게 섭취 가능함</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>특정 맛의 약 냄새 — 오렌지맛 제품의 경우 약간의 약 맛이 감돌아 아쉬움</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
     </row>
@@ -5336,12 +5201,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[김우빈 PICK] 종근당건강 아임비타 멀티비타민 컴팩트 30정 30일분</t>
+          <t>대웅제약 멀티비타민 미네랄 30정 30일분</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -5351,35 +5216,31 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591581101&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000135&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260601/nkEyZw9TcKRMHbTvSy6D591581101_00_00nkEyZw9TcKRMHbTvSy6D.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/2ijoJLmHVT94XXIOZnda600000135_00_002ijoJLmHVT94XXIOZnda.png</t>
         </is>
       </c>
       <c r="I7" t="n">
         <v>4.8</v>
       </c>
       <c r="J7" t="n">
-        <v>795</v>
+        <v>3569</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>부담 없는 착한 가격 — 매우 저렴한 가격에 한 달 분량 비타민을 구매 가능함</t>
+          <t>3천 원의 극가성비 — 3,000원이라는 매우 저렴한 가격으로 구매가 가능함</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>하루 한 알 간편 복용 — 하루 한 알만 챙겨 먹으면 되므로 복용 관리가 용이함</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>적당한 알약 크기 — 알약 크기가 크지 않아서 삼키는 데 부담이 없음</t>
-        </is>
-      </c>
+          <t>작은 알약 크기 — 알약 크기가 작아 목넘김과 복용이 수월함</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
@@ -5387,7 +5248,7 @@
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -5395,58 +5256,54 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[신혜선 PICK] 동국 마이팝 홍삼＆비타B</t>
+          <t>종근당건강 락토핏 당케어</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>종근당건강</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911030&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591580761&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260623/xNJvNqGjAYp0B7f9QQ8M610911030_00_00xNJvNqGjAYp0B7f9QQ8M.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250610/qUVshiLfS5KUSiQ9T3cu591580761_00_05qUVshiLfS5KUSiQ9T3cu.jpg</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J8" t="n">
-        <v>132</v>
+        <v>792</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>피로 회복 도움 — 피곤할 때 1포씩 먹으면 컨디션 회복에 도움이 됨</t>
+          <t>배변 활동 개선 — 섭취 후 화장실을 잘 가게 되어 장 건강 관리에 도움 됨</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>면역력 관리 — 면역력이 저하되었을 때 챙겨 먹기 적합함</t>
+          <t>남녀노소 편한 섭취 — 복용이 간편하고 가격 부담이 적음</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>강한 입안 잔향 — 섭취 후 2~3시간 동안 입안에 특유의 향이 오래 남음</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -5454,12 +5311,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>대웅제약 비타민C 30정 30일분</t>
+          <t>자연관 정성담은 배도라지스틱 12포</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>자연관</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -5469,36 +5326,36 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000127&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=901762093&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/V0qSVbLLgSaCWbYWEu73600000127_00_00V0qSVbLLgSaCWbYWEu73.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260508/SdledEzpIdjdFFQW6W8g901762093_00_00SdledEzpIdjdFFQW6W8g.png</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J9" t="n">
-        <v>2761</v>
+        <v>910</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>최고의 가성비 — 매우 착한 가격에 구매할 수 있어 지속 복용하기 좋음</t>
+          <t>목 건강 관리에 효과적 — 환절기나 목이 칼칼할 때 차처럼 마시기 적합함</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>일일 섭취량 충족 — 간편하게 하루 필수 비타민C 권장량을 채울 수 있음</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>충실한 효능과 용량 — 용량과 효능 측면에서 모두 기대 이상의 만족을 줌</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>다양한 섭취 및 휴대 편의 — 스틱 형태로 휴대가 편하며 그대로 먹거나 따뜻한 물에 타 먹기 좋음</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>다소 강한 단맛 — 단맛이 다소 강하게 느껴질 수 있음</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
     </row>
@@ -5513,12 +5370,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>오브맘 스트레스,쉼 30일분</t>
+          <t>홀베리 유기농 레몬즙 10포</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>오브맘</t>
+          <t>홀베리</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -5528,34 +5385,34 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=913624078&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=965923434&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250519/LCCefMiAcRv8JhM7m90p913624078_00_00LCCefMiAcRv8JhM7m90p.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260305/6AQS4j3WbfucTbhmJ4ur965923434_00_006AQS4j3WbfucTbhmJ4ur.jpg</t>
         </is>
       </c>
       <c r="I10" t="n">
         <v>4.8</v>
       </c>
       <c r="J10" t="n">
-        <v>593</v>
+        <v>1621</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>심신 안정 및 긴장 완화 — 중요한 일 전 섭취 시 마음이 평온해지고 심장의 두근거림이 완화됨</t>
+          <t>높은 요리 및 음료 활용도 — 올리브유 혼합이나 각종 요리에 활용하기에 용이함</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>톡톡 터지는 바나나 맛 — 바나나맛 팝핑캔디 제형이라 입안에서 톡톡 터지는 재미가 있음</t>
+          <t>부담 없는 적당한 신맛 — 신맛이 있으나 속이 아플 정도는 아니어서 섭취하기 괜찮음</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>불호 강한 특이 맛 — 약 특유의 맛으로 인해 뜯어 먹기 망설여질 만큼 거부감이 듦</t>
+          <t>단일 레몬즙 맛의 아쉬움 — 자몽 혼합 제품에 비해 풍미가 다소 심심하게 느껴질 수 있음</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
@@ -5572,55 +5429,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>대웅제약 알파CD ZERO 15포 15일분</t>
+          <t>휴럼 하루한포 구증구포 흑삼제로 5포 5일분</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>휴럼</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000207&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=919157054&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20251202/sucQSlMc1DA4dsj6Qff6600000207_00_00sucQSlMc1DA4dsj6Qff6.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260327/zJhcupvR4JWL5xMXOnRP919157054_00_01zJhcupvR4JWL5xMXOnRP.jpg</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J11" t="n">
-        <v>566</v>
+        <v>381</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>배변 활동 촉진 — 섭취 후 화장실을 잘 가게 되어 배변에 도움이 됨</t>
+          <t>부담 없는 가격과 가성비 — 가격 부담이 없어 저렴하게 구매하기 좋음</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>과식 욕구 방지 — 맛있는 파인애플 맛으로 음식을 먹고 싶은 욕구를 눌러줌</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>스틱 포장의 편의성 — 들고 다니며 먹기 편한 스틱 타입이라 휴대가 용이함</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>식전 복용 시간 맞춤 — 식사 15분 전에 맞춰 챙겨 마시기가 다소 번거로움</t>
-        </is>
-      </c>
+          <t>간편한 스틱 복용 — 스틱 형태로 제작되어 복용하기 편함</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
     </row>
@@ -5735,42 +5584,42 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>마그네슘</t>
-        </is>
-      </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>홍삼/인삼</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>멀티비타민/종합비타민</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>멀티비타민/종합비타민</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>홍삼/인삼</t>
-        </is>
-      </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -5792,52 +5641,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>종근당</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>동화약품</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
+          <t>익스트림</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>오브맘</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>종근당건강</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>자연관</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>락피도</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>종근당건강</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>동국제약</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>오브맘</t>
+          <t>홀베리</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>휴럼</t>
         </is>
       </c>
     </row>
@@ -5849,52 +5698,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>종근당 데일리와이즈 포스트바이오틱스 구미 7일분</t>
+          <t>[김종국 PICK] 익스트림 아르기닌 에너지온 2개입 2일분</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>동화 바이마그랩 마그네슘 식이섬유 5포 5일분</t>
+          <t>[다영 PICK] 셀트리온 브로멜라인＆알파 CD 30정 15일분</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>동국 맛있는 샐러드 미니볼 비타 15포 15일분</t>
+          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>[홍삼매니아] 자연관 홍삼정 에너타임 10포 10일분</t>
+          <t>[우형재 PICK] 익스트림 모노크레아틴 플러스 120 g 40일분</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>락피도 티니핑 면역스틱 12포 12일분</t>
+          <t>오브맘 활력에너지B 하루구미 30일분</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>[김우빈 PICK] 종근당건강 아임비타 멀티비타민 컴팩트 30정 30일분</t>
+          <t>대웅제약 멀티비타민 미네랄 30정 30일분</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>[신혜선 PICK] 동국 마이팝 홍삼＆비타B</t>
+          <t>종근당건강 락토핏 당케어</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 비타민C 30정 30일분</t>
+          <t>자연관 정성담은 배도라지스틱 12포</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>오브맘 스트레스,쉼 30일분</t>
+          <t>홀베리 유기농 레몬즙 10포</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 알파CD ZERO 15포 15일분</t>
+          <t>휴럼 하루한포 구증구포 흑삼제로 5포 5일분</t>
         </is>
       </c>
     </row>
@@ -5911,28 +5760,28 @@
         <v>4.7</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="I6" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J6" s="3" t="n">
         <v>4.7</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>4.8</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="7">
@@ -5942,37 +5791,37 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>341</v>
+        <v>805</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>514</v>
+        <v>903</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1519</v>
+        <v>2712</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1103</v>
+        <v>714</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>654</v>
+        <v>756</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>795</v>
+        <v>3569</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>132</v>
+        <v>792</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>2761</v>
+        <v>910</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>593</v>
+        <v>1621</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="8" ht="90" customHeight="1">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
@@ -5980,66 +5829,61 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>맛있는 요구르트 맛 — 요구르트 맛이 나서 질리지 않고 맛있게 먹을 수 있음
-건강한 간식 대용 — 몸에 해로운 일반 과자 대신 건강하게 간식으로 먹기 좋음</t>
+          <t>뛰어난 가성비 — 가격이 저렴하여 부담 없이 구매하기 좋음
+높은 재구매 만족도 — 제품 품질에 만족하여 지속적으로 재주문함</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>우수한 가성비 — 가격이 매우 저렴하여 매일 부담 없이 복용 가능함
-피로 회복 기대 — 마그네슘 성분 덕에 피로 회복에 어느 정도 도움이 됨</t>
+          <t>편리한 복용성 — 알약 형태라 먹기 편하고 체중 관리에 도움을 줌</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>간편한 간식 대용 — 맛있고 간편해서 허기질 때나 출출할 때 먹기 좋음
-합리적인 가성비 — 저렴한 가격 덕분에 아이들 간식용으로 재구매하기 좋음</t>
+          <t>부담 없는 커피 맛 — 카페인 부담이 적고 진한 커피 맛이 나 커피 대체용으로 좋음
+변비 개선 보조 — 꾸준히 마실 경우 변비 해소에 도움을 줌</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>활력 증진 체감 — 섭취 후 피로가 풀리고 몸의 활력이 느껴져 만족함
-뛰어난 가성비 — 저렴한 가격임에도 홍삼 제품 본연의 기능에 충실함
-간편한 섭취 방식 — 스틱 형태로 어디서나 가볍게 섭취하기 편리함</t>
+          <t>압도적인 가성비 — 타 플랫폼 제품 대비 가격 경쟁력이 매우 뛰어남
+간편한 섭취 방식 — 계량 스쿱 등으로 간편하게 떠먹기 편리함</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>아이들의 높은 선호도 — 기호성이 높아 아이들이 거부감 없이 먼저 찾아 먹음
-맛있는 젤리 제형 — 망고맛 젤리 형태라 간식처럼 즐겁게 먹일 수 있음</t>
+          <t>맛있는 구미 제형 — 약 같은 맛 없이 맛있는 젤리 형태로 즐길 수 있음
+간편한 영양 챙김 — 구미 타입이라 거부감 없이 간편하게 섭취 가능함</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>부담 없는 착한 가격 — 매우 저렴한 가격에 한 달 분량 비타민을 구매 가능함
-하루 한 알 간편 복용 — 하루 한 알만 챙겨 먹으면 되므로 복용 관리가 용이함
-적당한 알약 크기 — 알약 크기가 크지 않아서 삼키는 데 부담이 없음</t>
+          <t>3천 원의 극가성비 — 3,000원이라는 매우 저렴한 가격으로 구매가 가능함
+작은 알약 크기 — 알약 크기가 작아 목넘김과 복용이 수월함</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>피로 회복 도움 — 피곤할 때 1포씩 먹으면 컨디션 회복에 도움이 됨
-면역력 관리 — 면역력이 저하되었을 때 챙겨 먹기 적합함</t>
+          <t>배변 활동 개선 — 섭취 후 화장실을 잘 가게 되어 장 건강 관리에 도움 됨
+남녀노소 편한 섭취 — 복용이 간편하고 가격 부담이 적음</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>최고의 가성비 — 매우 착한 가격에 구매할 수 있어 지속 복용하기 좋음
-일일 섭취량 충족 — 간편하게 하루 필수 비타민C 권장량을 채울 수 있음
-충실한 효능과 용량 — 용량과 효능 측면에서 모두 기대 이상의 만족을 줌</t>
+          <t>목 건강 관리에 효과적 — 환절기나 목이 칼칼할 때 차처럼 마시기 적합함
+다양한 섭취 및 휴대 편의 — 스틱 형태로 휴대가 편하며 그대로 먹거나 따뜻한 물에 타 먹기 좋음</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>심신 안정 및 긴장 완화 — 중요한 일 전 섭취 시 마음이 평온해지고 심장의 두근거림이 완화됨
-톡톡 터지는 바나나 맛 — 바나나맛 팝핑캔디 제형이라 입안에서 톡톡 터지는 재미가 있음</t>
+          <t>높은 요리 및 음료 활용도 — 올리브유 혼합이나 각종 요리에 활용하기에 용이함
+부담 없는 적당한 신맛 — 신맛이 있으나 속이 아플 정도는 아니어서 섭취하기 괜찮음</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>배변 활동 촉진 — 섭취 후 화장실을 잘 가게 되어 배변에 도움이 됨
-과식 욕구 방지 — 맛있는 파인애플 맛으로 음식을 먹고 싶은 욕구를 눌러줌
-스틱 포장의 편의성 — 들고 다니며 먹기 편한 스틱 타입이라 휴대가 용이함</t>
+          <t>부담 없는 가격과 가성비 — 가격 부담이 없어 저렴하게 구매하기 좋음
+간편한 스틱 복용 — 스틱 형태로 제작되어 복용하기 편함</t>
         </is>
       </c>
     </row>
@@ -6049,44 +5893,32 @@
           <t>부정리뷰</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>적은 제품 용량 — 용량이 다소 적어서 빠르게 소비하게 됨</t>
-        </is>
-      </c>
+      <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>변비 개선 미흡 — 피로 회복과 달리 변비 관련 효과는 크게 느끼기 어려움</t>
+          <t>아쉬운 재구매 의사 — 특별한 체감 효과가 부족하여 재구매로 이어지지 않음</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>단단한 제형 식감 — 제형이 다소 딱딱하여 씹어 먹을 때 불편함이 있음</t>
+          <t>잦은 제품 품절 — 구매하려 할 때 품절인 경우가 많아 재구매가 어려움</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>특정 맛의 약 냄새 — 오렌지맛 제품의 경우 약간의 약 맛이 감돌아 아쉬움</t>
-        </is>
-      </c>
+      <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>강한 입안 잔향 — 섭취 후 2~3시간 동안 입안에 특유의 향이 오래 남음</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>다소 강한 단맛 — 단맛이 다소 강하게 느껴질 수 있음</t>
+        </is>
+      </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>불호 강한 특이 맛 — 약 특유의 맛으로 인해 뜯어 먹기 망설여질 만큼 거부감이 듦</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>식전 복용 시간 맞춤 — 식사 15분 전에 맞춰 챙겨 마시기가 다소 번거로움</t>
-        </is>
-      </c>
+          <t>단일 레몬즙 맛의 아쉬움 — 자몽 혼합 제품에 비해 풍미가 다소 심심하게 느껴질 수 있음</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="B10" s="1" t="inlineStr">
@@ -6096,7 +5928,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>1,000원</t>
+          <t>1,500원</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -6106,7 +5938,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -6126,22 +5958,22 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
           <t>2,000원</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
         </is>
       </c>
     </row>
@@ -6363,7 +6195,7 @@
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -6371,31 +6203,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+          <t>스파톤 애플 4종 (7일/14일/28일/42일)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>프로뉴트리션</t>
+          <t>스파톤</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>35,800원</t>
+          <t>7,500원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000229795&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549614ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022979501ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J3" t="n">
+        <v>346</v>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
@@ -6406,7 +6242,7 @@
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -6414,33 +6250,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>덴프스</t>
+          <t>프로뉴트리션</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>30,400원</t>
+          <t>35,800원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000206861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020686148ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549614ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>536</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>장 건강과 체지방 동시 관리 — 유산균을 통한 장 케어와 체지방 감소를 한 번에 관리 가능함</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>상큼한 요거트 맛 — 상큼한 요거트 맛으로 섭취 시 거부감이 없음</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -6480,8 +6328,12 @@
           <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="I5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J5" t="n">
+        <v>8318</v>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
@@ -6492,7 +6344,7 @@
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -6500,33 +6352,45 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>멜라메이트</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>16,900원</t>
+          <t>30,400원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000206861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355477ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020686148ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J6" t="n">
+        <v>24833</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>검증된 장 건강 개선 효과 — 꾸준히 섭취 시 장 건강 및 면역력 관리에 체감 효과가 높음</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>하루 한 알 간편 복용 — 하루 한 캡슐 섭취로 간편하게 관리할 수 있음</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -6566,10 +6430,22 @@
           <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018012128ko.jpg?l=ko</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="I7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J7" t="n">
+        <v>17016</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>확실한 붓기 완화 효과 — 야식 섭취 후나 촬영 전 얼굴 붓기를 빼는 데 효과적임</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>목넘김이 편한 미니환 — 환 크기가 작아 물과 함께 삼키기 수월함</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -6578,7 +6454,7 @@
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -6586,27 +6462,27 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>콜레올로지 PRO 600mg*30정/60정/120정 (15/30/60일분)</t>
+          <t>세노비스 루테인+오메가3 80캡슐 (+10캡슐 증정기획) (45일분)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>푸드올로지</t>
+          <t>세노비스</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>17,900원</t>
+          <t>25,900원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000175634&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000150476&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0017/A00000017563488ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0015/A00000015047614ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -6621,7 +6497,7 @@
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -6629,35 +6505,51 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>고려은단 메가도스C 비타민C 3000mg 100포 (100일분)</t>
+          <t>콜레올로지 PRO 600mg*30정/60정/120정 (15/30/60일분)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>고려은단</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>25,900원</t>
+          <t>17,900원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000225906&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000175634&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022590605ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0017/A00000017563488ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>26920</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>원활한 배변 및 뱃살 관리 — 답답한 속을 시원하게 해주고 뱃살 관리에 도움을 줌</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>아침 공복의 가벼운 컨디션 — 아침에 느껴지는 몸의 무거움을 줄여줌</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>다소 큰 알약 크기 — 알약 크기가 다소 커서 목넘김이 부담스러울 수 있음</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
     </row>
@@ -6672,33 +6564,45 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>코자아 식물성 멜라토닌 함유 젤리/드링크 (단품/기획)</t>
+          <t>[TWS PICK] 미에로화이바 데이톡 14포 (14일분)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>코자아</t>
+          <t>미에로화이바</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>36,000원</t>
+          <t>15,900원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000236755&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000237883&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0023/A00000023675540ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0023/A00000023788363ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>5</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2862</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>식후 더부룩함 해소 — 과식 후 팽만감과 더부룩함을 효과적으로 완화함</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>배변 및 중성지질 관리 — 배변 활동 촉진과 중성지질 관리를 동시에 지원함</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -6707,7 +6611,7 @@
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -6715,35 +6619,51 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 30입 (1개월분)</t>
+          <t>판도라 브이트리티 7/14+1포 (7/15일분)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>판도라</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>115,000원</t>
+          <t>24,500원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000207974&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000227334&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020797409ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022733451ko.png?l=ko</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>5</v>
+      </c>
+      <c r="J11" t="n">
+        <v>18913</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>탁월한 라인 및 붓기 케어 — 아침 붓기 완화와 얼굴/다리 라인 관리에 효과가 뛰어남</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>상큼한 포도 맛과 휴대성 — 액상 포 타입으로 휴대와 섭취가 간편하며 포도 맛이 남</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>은은한 한약 풍미 — 포도 맛 뒤에 약간의 한약 느낌이 섞여 있음</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
     </row>
@@ -6863,47 +6783,47 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>프로바이오틱스/유산균</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>프로바이오틱스/유산균</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>루테인/눈건강</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>비타민C/항산화</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
     </row>
@@ -6920,24 +6840,24 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
+          <t>스파톤</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
           <t>프로뉴트리션</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>덴프스</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>덴프스</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>멜라메이트</t>
-        </is>
-      </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
           <t>생활약속</t>
@@ -6945,22 +6865,22 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>세노비스</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>푸드올로지</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>고려은단</t>
-        </is>
-      </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>코자아</t>
+          <t>미에로화이바</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>판도라</t>
         </is>
       </c>
     </row>
@@ -6977,24 +6897,24 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>스파톤 애플 4종 (7일/14일/28일/42일)</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
-        </is>
-      </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
           <t>[곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
@@ -7002,22 +6922,22 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
+          <t>세노비스 루테인+오메가3 80캡슐 (+10캡슐 증정기획) (45일분)</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
           <t>콜레올로지 PRO 600mg*30정/60정/120정 (15/30/60일분)</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>고려은단 메가도스C 비타민C 3000mg 100포 (100일분)</t>
-        </is>
-      </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>코자아 식물성 멜라토닌 함유 젤리/드링크 (단품/기획)</t>
+          <t>[TWS PICK] 미에로화이바 데이톡 14포 (14일분)</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 30입 (1개월분)</t>
+          <t>판도라 브이트리티 7/14+1포 (7/15일분)</t>
         </is>
       </c>
     </row>
@@ -7028,15 +6948,31 @@
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr"/>
-      <c r="D6" s="3" t="inlineStr"/>
-      <c r="E6" s="3" t="inlineStr"/>
-      <c r="F6" s="3" t="inlineStr"/>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr"/>
+      <c r="D6" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>4.8</v>
+      </c>
       <c r="I6" s="3" t="inlineStr"/>
-      <c r="J6" s="3" t="inlineStr"/>
-      <c r="K6" s="3" t="inlineStr"/>
-      <c r="L6" s="3" t="inlineStr"/>
+      <c r="J6" s="3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="7">
       <c r="B7" s="1" t="inlineStr">
@@ -7045,17 +6981,33 @@
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr"/>
+      <c r="D7" s="3" t="n">
+        <v>346</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>536</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>8318</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>24833</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>17016</v>
+      </c>
       <c r="I7" s="3" t="inlineStr"/>
-      <c r="J7" s="3" t="inlineStr"/>
-      <c r="K7" s="3" t="inlineStr"/>
-      <c r="L7" s="3" t="inlineStr"/>
-    </row>
-    <row r="8">
+      <c r="J7" s="3" t="n">
+        <v>26920</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>2862</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>18913</v>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
@@ -7063,14 +7015,44 @@
       </c>
       <c r="C8" s="3" t="inlineStr"/>
       <c r="D8" s="3" t="inlineStr"/>
-      <c r="E8" s="3" t="inlineStr"/>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>장 건강과 체지방 동시 관리 — 유산균을 통한 장 케어와 체지방 감소를 한 번에 관리 가능함
+상큼한 요거트 맛 — 상큼한 요거트 맛으로 섭취 시 거부감이 없음</t>
+        </is>
+      </c>
       <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>검증된 장 건강 개선 효과 — 꾸준히 섭취 시 장 건강 및 면역력 관리에 체감 효과가 높음
+하루 한 알 간편 복용 — 하루 한 캡슐 섭취로 간편하게 관리할 수 있음</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>확실한 붓기 완화 효과 — 야식 섭취 후나 촬영 전 얼굴 붓기를 빼는 데 효과적임
+목넘김이 편한 미니환 — 환 크기가 작아 물과 함께 삼키기 수월함</t>
+        </is>
+      </c>
       <c r="I8" s="3" t="inlineStr"/>
-      <c r="J8" s="3" t="inlineStr"/>
-      <c r="K8" s="3" t="inlineStr"/>
-      <c r="L8" s="3" t="inlineStr"/>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>원활한 배변 및 뱃살 관리 — 답답한 속을 시원하게 해주고 뱃살 관리에 도움을 줌
+아침 공복의 가벼운 컨디션 — 아침에 느껴지는 몸의 무거움을 줄여줌</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>식후 더부룩함 해소 — 과식 후 팽만감과 더부룩함을 효과적으로 완화함
+배변 및 중성지질 관리 — 배변 활동 촉진과 중성지질 관리를 동시에 지원함</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>탁월한 라인 및 붓기 케어 — 아침 붓기 완화와 얼굴/다리 라인 관리에 효과가 뛰어남
+상큼한 포도 맛과 휴대성 — 액상 포 타입으로 휴대와 섭취가 간편하며 포도 맛이 남</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="B9" s="1" t="inlineStr">
@@ -7085,9 +7067,17 @@
       <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr"/>
-      <c r="J9" s="3" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>다소 큰 알약 크기 — 알약 크기가 다소 커서 목넘김이 부담스러울 수 있음</t>
+        </is>
+      </c>
       <c r="K9" s="3" t="inlineStr"/>
-      <c r="L9" s="3" t="inlineStr"/>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>은은한 한약 풍미 — 포도 맛 뒤에 약간의 한약 느낌이 섞여 있음</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="1" t="inlineStr">
@@ -7102,24 +7092,24 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
+          <t>7,500원</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
           <t>35,800원</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>31,400원</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>30,400원</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>31,400원</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>16,900원</t>
-        </is>
-      </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
           <t>16,200원</t>
@@ -7127,22 +7117,22 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
+          <t>25,900원</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
           <t>17,900원</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>25,900원</t>
-        </is>
-      </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>36,000원</t>
+          <t>15,900원</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>115,000원</t>
+          <t>24,500원</t>
         </is>
       </c>
     </row>
@@ -7230,7 +7220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7272,98 +7262,98 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C2" t="n">
-        <v>32.5</v>
+        <v>37.5</v>
       </c>
       <c r="D2" t="n">
         <v>4</v>
       </c>
       <c r="E2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F2" t="n">
         <v>5</v>
-      </c>
-      <c r="F2" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>25</v>
+        <v>27.5</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="B4" t="n">
+        <v>9</v>
+      </c>
+      <c r="C4" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="D4" t="n">
         <v>8</v>
       </c>
-      <c r="C4" t="n">
-        <v>20</v>
-      </c>
-      <c r="D4" t="n">
-        <v>6</v>
-      </c>
       <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
         <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
         <v>2</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -7372,35 +7362,35 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
         <v>0</v>
       </c>
-      <c r="E7" t="n">
-        <v>1</v>
-      </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -7410,34 +7400,12 @@
         <v>2.5</v>
       </c>
       <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
         <v>0</v>
       </c>
-      <c r="E8" t="n">
-        <v>1</v>
-      </c>
       <c r="F8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>피부/미용</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
         <v>0</v>
       </c>
     </row>
